--- a/artfynd/A 14365-2025 artfynd.xlsx
+++ b/artfynd/A 14365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124467491</v>
+        <v>110026360</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99059</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,57 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>219792</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Adam och eva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dactylorhiza sambucina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Löten, Upl</t>
+          <t>Vagn, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>698112</v>
+        <v>698042</v>
       </c>
       <c r="R2" t="n">
-        <v>6645893</v>
+        <v>6645872</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,17 +760,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-26</t>
+          <t>2023-06-11</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Labyrintiskt hymenium = P. chrysoloma s.s.</t>
+          <t>Betad hage</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,21 +779,216 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gabriel Ekman</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124468950</v>
+      </c>
+      <c r="B3" t="n">
+        <v>103683</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Löten, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>698054</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6645864</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-26</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Viktor Lund</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Viktor Lund, Joakim Ekman, Martin Axegård</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>76293314</v>
+      </c>
+      <c r="B4" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vagn, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>698045</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6645874</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edsbro</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-07-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Niina Sallmén</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 14365-2025 artfynd.xlsx
+++ b/artfynd/A 14365-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110026360</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124468950</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,8 +1004,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/76293314</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>